--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481951</v>
+        <v>121481902</v>
       </c>
       <c r="B2" t="n">
-        <v>90709</v>
+        <v>78604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520369</v>
+        <v>520386</v>
       </c>
       <c r="R2" t="n">
-        <v>6967890</v>
+        <v>6967934</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121481902</v>
+        <v>121481856</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>79685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520386</v>
+        <v>520367</v>
       </c>
       <c r="R3" t="n">
-        <v>6967934</v>
+        <v>6967959</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481856</v>
+        <v>121481951</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>90710</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520367</v>
+        <v>520369</v>
       </c>
       <c r="R4" t="n">
-        <v>6967959</v>
+        <v>6967890</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481902</v>
+        <v>121481951</v>
       </c>
       <c r="B2" t="n">
-        <v>78604</v>
+        <v>90713</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520386</v>
+        <v>520369</v>
       </c>
       <c r="R2" t="n">
-        <v>6967934</v>
+        <v>6967890</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>121481856</v>
       </c>
       <c r="B3" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481951</v>
+        <v>121481902</v>
       </c>
       <c r="B4" t="n">
-        <v>90710</v>
+        <v>78607</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520369</v>
+        <v>520386</v>
       </c>
       <c r="R4" t="n">
-        <v>6967890</v>
+        <v>6967934</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481951</v>
+        <v>121481856</v>
       </c>
       <c r="B2" t="n">
-        <v>90713</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520369</v>
+        <v>520367</v>
       </c>
       <c r="R2" t="n">
-        <v>6967890</v>
+        <v>6967959</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121481856</v>
+        <v>121481951</v>
       </c>
       <c r="B3" t="n">
-        <v>79688</v>
+        <v>90713</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520367</v>
+        <v>520369</v>
       </c>
       <c r="R3" t="n">
-        <v>6967959</v>
+        <v>6967890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481856</v>
+        <v>121481902</v>
       </c>
       <c r="B2" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520367</v>
+        <v>520386</v>
       </c>
       <c r="R2" t="n">
-        <v>6967959</v>
+        <v>6967934</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121481951</v>
+        <v>121481856</v>
       </c>
       <c r="B3" t="n">
-        <v>90713</v>
+        <v>79689</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520369</v>
+        <v>520367</v>
       </c>
       <c r="R3" t="n">
-        <v>6967890</v>
+        <v>6967959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481902</v>
+        <v>121481951</v>
       </c>
       <c r="B4" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520386</v>
+        <v>520369</v>
       </c>
       <c r="R4" t="n">
-        <v>6967934</v>
+        <v>6967890</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481902</v>
+        <v>121481856</v>
       </c>
       <c r="B2" t="n">
-        <v>78608</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520386</v>
+        <v>520367</v>
       </c>
       <c r="R2" t="n">
-        <v>6967934</v>
+        <v>6967959</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121481856</v>
+        <v>121481951</v>
       </c>
       <c r="B3" t="n">
-        <v>79689</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520367</v>
+        <v>520369</v>
       </c>
       <c r="R3" t="n">
-        <v>6967959</v>
+        <v>6967890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481951</v>
+        <v>121481902</v>
       </c>
       <c r="B4" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520369</v>
+        <v>520386</v>
       </c>
       <c r="R4" t="n">
-        <v>6967890</v>
+        <v>6967934</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481856</v>
+        <v>121481951</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520367</v>
+        <v>520369</v>
       </c>
       <c r="R2" t="n">
-        <v>6967959</v>
+        <v>6967890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121481951</v>
+        <v>121481856</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520369</v>
+        <v>520367</v>
       </c>
       <c r="R3" t="n">
-        <v>6967890</v>
+        <v>6967959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481951</v>
+        <v>121481902</v>
       </c>
       <c r="B2" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520369</v>
+        <v>520386</v>
       </c>
       <c r="R2" t="n">
-        <v>6967890</v>
+        <v>6967934</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121481856</v>
+        <v>121481951</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>90720</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520367</v>
+        <v>520369</v>
       </c>
       <c r="R3" t="n">
-        <v>6967959</v>
+        <v>6967890</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481902</v>
+        <v>121481856</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520386</v>
+        <v>520367</v>
       </c>
       <c r="R4" t="n">
-        <v>6967934</v>
+        <v>6967959</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481902</v>
+        <v>121481856</v>
       </c>
       <c r="B2" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520386</v>
+        <v>520367</v>
       </c>
       <c r="R2" t="n">
-        <v>6967934</v>
+        <v>6967959</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481856</v>
+        <v>121481902</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520367</v>
+        <v>520386</v>
       </c>
       <c r="R4" t="n">
-        <v>6967959</v>
+        <v>6967934</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481856</v>
+        <v>121481902</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520367</v>
+        <v>520386</v>
       </c>
       <c r="R2" t="n">
-        <v>6967959</v>
+        <v>6967934</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121481951</v>
+        <v>121481856</v>
       </c>
       <c r="B3" t="n">
-        <v>90720</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520369</v>
+        <v>520367</v>
       </c>
       <c r="R3" t="n">
-        <v>6967890</v>
+        <v>6967959</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481902</v>
+        <v>121481951</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520386</v>
+        <v>520369</v>
       </c>
       <c r="R4" t="n">
-        <v>6967934</v>
+        <v>6967890</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481902</v>
+        <v>121481856</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520386</v>
+        <v>520367</v>
       </c>
       <c r="R2" t="n">
-        <v>6967934</v>
+        <v>6967959</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481856</v>
+        <v>121481902</v>
       </c>
       <c r="B4" t="n">
-        <v>79697</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520367</v>
+        <v>520386</v>
       </c>
       <c r="R4" t="n">
-        <v>6967959</v>
+        <v>6967934</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121481951</v>
+        <v>121481902</v>
       </c>
       <c r="B3" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520369</v>
+        <v>520386</v>
       </c>
       <c r="R3" t="n">
-        <v>6967890</v>
+        <v>6967934</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481902</v>
+        <v>121481951</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520386</v>
+        <v>520369</v>
       </c>
       <c r="R4" t="n">
-        <v>6967934</v>
+        <v>6967890</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121481856</v>
+        <v>121481951</v>
       </c>
       <c r="B2" t="n">
-        <v>79697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520367</v>
+        <v>520369</v>
       </c>
       <c r="R2" t="n">
-        <v>6967959</v>
+        <v>6967890</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +785,11 @@
         <v>121481902</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121481951</v>
+        <v>121481856</v>
       </c>
       <c r="B4" t="n">
-        <v>90728</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520369</v>
+        <v>520367</v>
       </c>
       <c r="R4" t="n">
-        <v>6967890</v>
+        <v>6967959</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 57105-2024 artfynd.xlsx
+++ b/artfynd/A 57105-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121481951</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121481902</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121481856</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>